--- a/outputs/analysis/Orlistat/extracted_trials/Orlistat_Clinical_Cohort_extracted.xlsx
+++ b/outputs/analysis/Orlistat/extracted_trials/Orlistat_Clinical_Cohort_extracted.xlsx
@@ -140,6 +140,216 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -502,26 +712,18 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>2024</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -535,6 +737,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -640,7 +843,6 @@
           <t>between</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>18</v>
       </c>
@@ -663,6 +865,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -798,35 +1001,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>5.29</v>
       </c>
       <c r="J2" t="n">
         <v>0.92</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>5</v>
       </c>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>TC (mmol/L) 5.29 ± 0.92 5.17 ± 0.87 5.41 ± 0.97 0.289</t>
@@ -844,35 +1032,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>5.17</v>
       </c>
       <c r="J3" t="n">
         <v>0.87</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
         <v>5</v>
       </c>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>TC (mmol/L) 5.29 ± 0.92 5.17 ± 0.87 5.41 ± 0.97 0.289</t>
@@ -890,35 +1063,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>5.41</v>
       </c>
       <c r="J4" t="n">
         <v>0.97</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>TC (mmol/L) 5.29 ± 0.92 5.17 ± 0.87 5.41 ± 0.97 0.289</t>
@@ -936,35 +1094,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>1.02</v>
       </c>
       <c r="J5" t="n">
         <v>0.15</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>HDL (mmol/L) 1.02 ± 0.15 0.99 ± 0.15 1.04 ± 0.16 0.137</t>
@@ -982,35 +1125,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>0.99</v>
       </c>
       <c r="J6" t="n">
         <v>0.15</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>HDL (mmol/L) 1.02 ± 0.15 0.99 ± 0.15 1.04 ± 0.16 0.137</t>
@@ -1028,35 +1156,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>1.04</v>
       </c>
       <c r="J7" t="n">
         <v>0.16</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>HDL (mmol/L) 1.02 ± 0.15 0.99 ± 0.15 1.04 ± 0.16 0.137</t>
@@ -1074,35 +1187,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>3.48</v>
       </c>
       <c r="J8" t="n">
         <v>0.73</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>LDL (mmol/L) 3.48 ± 0.73 3.34 ± 0.68 3.62 ± 0.77 0.106</t>
@@ -1120,35 +1218,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>3.34</v>
       </c>
       <c r="J9" t="n">
         <v>0.68</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>LDL (mmol/L) 3.48 ± 0.73 3.34 ± 0.68 3.62 ± 0.77 0.106</t>
@@ -1166,35 +1249,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>3.62</v>
       </c>
       <c r="J10" t="n">
         <v>0.77</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>LDL (mmol/L) 3.48 ± 0.73 3.34 ± 0.68 3.62 ± 0.77 0.106</t>
@@ -1212,35 +1280,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>2.49</v>
       </c>
       <c r="J11" t="n">
         <v>1.09</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>TG (mmol/L) 2.49 ± 1.09 2.47 ± 0.94 2.52 ± 1.23 0.844</t>
@@ -1258,35 +1311,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>2.47</v>
       </c>
       <c r="J12" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>TG (mmol/L) 2.49 ± 1.09 2.47 ± 0.94 2.52 ± 1.23 0.844</t>
@@ -1304,35 +1342,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>2.52</v>
       </c>
       <c r="J13" t="n">
         <v>1.23</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
       <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>TG (mmol/L) 2.49 ± 1.09 2.47 ± 0.94 2.52 ± 1.23 0.844</t>
@@ -1350,35 +1373,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>5.09</v>
       </c>
       <c r="J14" t="n">
         <v>0.49</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
       <c r="T14" t="n">
         <v>5</v>
       </c>
-      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) 5.09 ± 0.49 5.09 ± 0.49 5.09 ± 0.50 0.964</t>
@@ -1396,35 +1404,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>5.09</v>
       </c>
       <c r="J15" t="n">
         <v>0.49</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
         <v>5</v>
       </c>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) 5.09 ± 0.49 5.09 ± 0.49 5.09 ± 0.50 0.964</t>
@@ -1442,35 +1435,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>5.09</v>
       </c>
       <c r="J16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
         <v>5</v>
       </c>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) 5.09 ± 0.49 5.09 ± 0.49 5.09 ± 0.50 0.964</t>
@@ -1488,35 +1466,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>55.11</v>
       </c>
       <c r="J17" t="n">
         <v>33.04</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
         <v>5</v>
       </c>
-      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>ALT (U/L) 55.11 ± 33.04 52.82 ± 35.89 57.33 ± 30.35 0.569</t>
@@ -1534,35 +1497,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>52.82</v>
       </c>
       <c r="J18" t="n">
         <v>35.89</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
         <v>5</v>
       </c>
-      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>ALT (U/L) 55.11 ± 33.04 52.82 ± 35.89 57.33 ± 30.35 0.569</t>
@@ -1580,35 +1528,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>57.33</v>
       </c>
       <c r="J19" t="n">
         <v>30.35</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
       <c r="T19" t="n">
         <v>5</v>
       </c>
-      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>ALT (U/L) 55.11 ± 33.04 52.82 ± 35.89 57.33 ± 30.35 0.569</t>
@@ -1626,35 +1559,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>4.45</v>
       </c>
       <c r="J20" t="n">
         <v>1.08</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
         <v>5</v>
       </c>
-      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>Urea (mmol/L) 4.45 ± 1.08 4.36 ± 1.22 4.54 ± 0.93 0.492</t>
@@ -1672,35 +1590,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>4.36</v>
       </c>
       <c r="J21" t="n">
         <v>1.22</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
       <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
           <t>Urea (mmol/L) 4.45 ± 1.08 4.36 ± 1.22 4.54 ± 0.93 0.492</t>
@@ -1718,35 +1621,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>4.54</v>
       </c>
       <c r="J22" t="n">
         <v>0.93</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
         <v>5</v>
       </c>
-      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>Urea (mmol/L) 4.45 ± 1.08 4.36 ± 1.22 4.54 ± 0.93 0.492</t>
@@ -1764,35 +1652,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>9.52</v>
       </c>
       <c r="J23" t="n">
         <v>1.6</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
       <c r="T23" t="n">
         <v>5</v>
       </c>
-      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>Uric acid (mg/dl) 9.52 ± 1.60 9.51 ± 1.51 9.53 ± 1.81 0.956</t>
@@ -1810,35 +1683,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>9.51</v>
       </c>
       <c r="J24" t="n">
         <v>1.51</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
       <c r="T24" t="n">
         <v>5</v>
       </c>
-      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
           <t>Uric acid (mg/dl) 9.52 ± 1.60 9.51 ± 1.51 9.53 ± 1.81 0.956</t>
@@ -1856,35 +1714,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>9.529999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>1.81</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
         <v>5</v>
       </c>
-      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
           <t>Uric acid (mg/dl) 9.52 ± 1.60 9.51 ± 1.51 9.53 ± 1.81 0.956</t>
@@ -1902,35 +1745,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>3.67</v>
       </c>
       <c r="J26" t="n">
         <v>3.88</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
         <v>5</v>
       </c>
-      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>Aggregates 3.67 ± 3.88 3.61 ± 3.90 3.73 ± 3.91 0.905</t>
@@ -1948,35 +1776,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>3.61</v>
       </c>
       <c r="J27" t="n">
         <v>3.9</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
         <v>5</v>
       </c>
-      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>Aggregates 3.67 ± 3.88 3.61 ± 3.90 3.73 ± 3.91 0.905</t>
@@ -1994,35 +1807,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>3.73</v>
       </c>
       <c r="J28" t="n">
         <v>3.91</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
       <c r="T28" t="n">
         <v>5</v>
       </c>
-      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
           <t>Aggregates 3.67 ± 3.88 3.61 ± 3.90 3.73 ± 3.91 0.905</t>
@@ -2040,35 +1838,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>1.15</v>
       </c>
       <c r="J29" t="n">
         <v>2.67</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
       <c r="T29" t="n">
         <v>5</v>
       </c>
-      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>Double contour sign 1.15 ± 2.67 1.10 ± 2.68 1.20 ± 2.71 0.945</t>
@@ -2086,35 +1869,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>2.68</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
       <c r="T30" t="n">
         <v>5</v>
       </c>
-      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>Double contour sign 1.15 ± 2.67 1.10 ± 2.68 1.20 ± 2.71 0.945</t>
@@ -2132,35 +1900,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>2.71</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
       <c r="T31" t="n">
         <v>5</v>
       </c>
-      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
           <t>Double contour sign 1.15 ± 2.67 1.10 ± 2.68 1.20 ± 2.71 0.945</t>
@@ -2178,35 +1931,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
         <v>1.15</v>
       </c>
       <c r="J32" t="n">
         <v>2.99</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" t="n">
         <v>5</v>
       </c>
-      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>Tophus 1.15 ± 2.99 1.13 ± 3.00 1.17 ± 3.04 0.961</t>
@@ -2224,35 +1962,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
         <v>1.13</v>
       </c>
       <c r="J33" t="n">
         <v>3</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
       <c r="T33" t="n">
         <v>5</v>
       </c>
-      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>Tophus 1.15 ± 2.99 1.13 ± 3.00 1.17 ± 3.04 0.961</t>
@@ -2270,35 +1993,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>1.17</v>
       </c>
       <c r="J34" t="n">
         <v>3.04</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
         <v>5</v>
       </c>
-      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>Tophus 1.15 ± 2.99 1.13 ± 3.00 1.17 ± 3.04 0.961</t>
@@ -2316,35 +2024,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
         <v>628.01</v>
       </c>
       <c r="J35" t="n">
         <v>93.97</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
       <c r="T35" t="n">
         <v>5</v>
       </c>
-      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>The highest uric acid before (µmol/L) 628.01 ± 93.97 630.03 ± 94.57 626.22 ± 94.74 0.869</t>
@@ -2362,35 +2055,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
         <v>630.03</v>
       </c>
       <c r="J36" t="n">
         <v>94.56999999999999</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
       <c r="T36" t="n">
         <v>5</v>
       </c>
-      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
           <t>The highest uric acid before (µmol/L) 628.01 ± 93.97 630.03 ± 94.57 626.22 ± 94.74 0.869</t>
@@ -2408,35 +2086,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
         <v>626.22</v>
       </c>
       <c r="J37" t="n">
         <v>94.73999999999999</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
       <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>The highest uric acid before (µmol/L) 628.01 ± 93.97 630.03 ± 94.57 626.22 ± 94.74 0.869</t>
@@ -2454,35 +2117,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>1.92</v>
       </c>
       <c r="J38" t="n">
         <v>2.59</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
       <c r="T38" t="n">
         <v>6</v>
       </c>
-      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>Weight (kg) -1.92 ± 2.59 -0.76 ± 2.37 -2.85 ± 2.37 0.001</t>
@@ -2500,35 +2148,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>0.76</v>
       </c>
       <c r="J39" t="n">
         <v>2.37</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
       <c r="T39" t="n">
         <v>6</v>
       </c>
-      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>Weight (kg) -1.92 ± 2.59 -0.76 ± 2.37 -2.85 ± 2.37 0.001</t>
@@ -2546,35 +2179,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>2.85</v>
       </c>
       <c r="J40" t="n">
         <v>2.37</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
       <c r="T40" t="n">
         <v>6</v>
       </c>
-      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>Weight (kg) -1.92 ± 2.59 -0.76 ± 2.37 -2.85 ± 2.37 0.001</t>
@@ -2592,35 +2210,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>0.63</v>
       </c>
       <c r="J41" t="n">
         <v>0.83</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
         <v>6</v>
       </c>
-      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
           <t>BMI (kg/m2) -0.63 ± 0.83 -0.25 ± 0.75 -0.95 ± 0.77 0.001</t>
@@ -2638,35 +2241,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>0.25</v>
       </c>
       <c r="J42" t="n">
         <v>0.75</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
       <c r="T42" t="n">
         <v>6</v>
       </c>
-      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
           <t>BMI (kg/m2) -0.63 ± 0.83 -0.25 ± 0.75 -0.95 ± 0.77 0.001</t>
@@ -2684,35 +2272,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>0.95</v>
       </c>
       <c r="J43" t="n">
         <v>0.77</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
       <c r="T43" t="n">
         <v>6</v>
       </c>
-      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>BMI (kg/m2) -0.63 ± 0.83 -0.25 ± 0.75 -0.95 ± 0.77 0.001</t>
@@ -2730,35 +2303,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>1.98</v>
       </c>
       <c r="J44" t="n">
         <v>2.67</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="n">
         <v>6</v>
       </c>
-      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>WC (cm) -1.98 ± 2.67 -0.75 ± 2.60 -2.97 ± 2.32 0.001</t>
@@ -2776,35 +2334,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>0.75</v>
       </c>
       <c r="J45" t="n">
         <v>2.6</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
       <c r="T45" t="n">
         <v>6</v>
       </c>
-      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
           <t>WC (cm) -1.98 ± 2.67 -0.75 ± 2.60 -2.97 ± 2.32 0.001</t>
@@ -2822,35 +2365,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>2.97</v>
       </c>
       <c r="J46" t="n">
         <v>2.32</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
         <v>6</v>
       </c>
-      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
           <t>WC (cm) -1.98 ± 2.67 -0.75 ± 2.60 -2.97 ± 2.32 0.001</t>
@@ -2868,35 +2396,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>1.39</v>
       </c>
       <c r="J47" t="n">
         <v>2.11</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
       <c r="T47" t="n">
         <v>6</v>
       </c>
-      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>Body fat (kg) -1.39 ± 2.11 -0.19 ± 1.69 -2.30 ± 1.95 &lt;0.001</t>
@@ -2914,35 +2427,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>0.19</v>
       </c>
       <c r="J48" t="n">
         <v>1.69</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
         <v>6</v>
       </c>
-      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
           <t>Body fat (kg) -1.39 ± 2.11 -0.19 ± 1.69 -2.30 ± 1.95 &lt;0.001</t>
@@ -2960,35 +2458,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>1.95</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
       <c r="T49" t="n">
         <v>6</v>
       </c>
-      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>Body fat (kg) -1.39 ± 2.11 -0.19 ± 1.69 -2.30 ± 1.95 &lt;0.001</t>
@@ -3006,35 +2489,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>0.42</v>
       </c>
       <c r="J50" t="n">
         <v>0.89</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
       <c r="T50" t="n">
         <v>6</v>
       </c>
-      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
           <t>Body muscle (kg) -0.42 ± 0.89 -0.09 ± 0.87 -0.67 ± 0.83 0.021</t>
@@ -3052,35 +2520,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>0.09</v>
       </c>
       <c r="J51" t="n">
         <v>0.87</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
       <c r="T51" t="n">
         <v>6</v>
       </c>
-      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
           <t>Body muscle (kg) -0.42 ± 0.89 -0.09 ± 0.87 -0.67 ± 0.83 0.021</t>
@@ -3098,35 +2551,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>0.67</v>
       </c>
       <c r="J52" t="n">
         <v>0.83</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
       <c r="T52" t="n">
         <v>6</v>
       </c>
-      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>Body muscle (kg) -0.42 ± 0.89 -0.09 ± 0.87 -0.67 ± 0.83 0.021</t>
@@ -3144,35 +2582,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>0.06</v>
       </c>
       <c r="J53" t="n">
         <v>0.5</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
       <c r="T53" t="n">
         <v>6</v>
       </c>
-      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) -0.06 ± 0.50 -0.03 ± 0.48 -0.07 ± 0.53 0.776</t>
@@ -3190,35 +2613,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>0.03</v>
       </c>
       <c r="J54" t="n">
         <v>0.48</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
       <c r="T54" t="n">
         <v>6</v>
       </c>
-      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) -0.06 ± 0.50 -0.03 ± 0.48 -0.07 ± 0.53 0.776</t>
@@ -3236,35 +2644,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0.53</v>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
       <c r="T55" t="n">
         <v>6</v>
       </c>
-      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) -0.06 ± 0.50 -0.03 ± 0.48 -0.07 ± 0.53 0.776</t>
@@ -3282,35 +2675,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>0.05</v>
       </c>
       <c r="J56" t="n">
         <v>0.13</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
       <c r="T56" t="n">
         <v>6</v>
       </c>
-      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
           <t>HDL (mmol/L) -0.05 ± 0.13 0.01 ± 0.13 -0.09 ± 0.10 0.002</t>
@@ -3328,35 +2706,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>0.01</v>
       </c>
       <c r="J57" t="n">
         <v>0.13</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
       <c r="T57" t="n">
         <v>6</v>
       </c>
-      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
           <t>HDL (mmol/L) -0.05 ± 0.13 0.01 ± 0.13 -0.09 ± 0.10 0.002</t>
@@ -3374,35 +2737,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>0.09</v>
       </c>
       <c r="J58" t="n">
         <v>0.1</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
       <c r="T58" t="n">
         <v>6</v>
       </c>
-      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
           <t>HDL (mmol/L) -0.05 ± 0.13 0.01 ± 0.13 -0.09 ± 0.10 0.002</t>
@@ -3420,35 +2768,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>0.39</v>
       </c>
       <c r="J59" t="n">
         <v>0.75</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
       <c r="T59" t="n">
         <v>6</v>
       </c>
-      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
           <t>TC (mmol/L) -0.39 ± 0.75 -0.10 ± 0.64 -0.61 ± 0.76 0.012</t>
@@ -3466,35 +2799,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0.1</v>
       </c>
       <c r="J60" t="n">
         <v>0.64</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
       <c r="T60" t="n">
         <v>6</v>
       </c>
-      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
           <t>TC (mmol/L) -0.39 ± 0.75 -0.10 ± 0.64 -0.61 ± 0.76 0.012</t>
@@ -3512,35 +2830,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.61</v>
       </c>
       <c r="J61" t="n">
         <v>0.76</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="n">
         <v>6</v>
       </c>
-      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
           <t>TC (mmol/L) -0.39 ± 0.75 -0.10 ± 0.64 -0.61 ± 0.76 0.012</t>
@@ -3558,35 +2861,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0.03</v>
       </c>
       <c r="J62" t="n">
         <v>7.38</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
       <c r="T62" t="n">
         <v>6</v>
       </c>
-      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
           <t>Creatinine (µmol/L) 0.03 ± 7.38 0.05 ± 7.02 -0.01 ± 7.75 0.983</t>
@@ -3604,35 +2892,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0.05</v>
       </c>
       <c r="J63" t="n">
         <v>7.02</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
       <c r="T63" t="n">
         <v>6</v>
       </c>
-      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
           <t>Creatinine (µmol/L) 0.03 ± 7.38 0.05 ± 7.02 -0.01 ± 7.75 0.983</t>
@@ -3650,35 +2923,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0.01</v>
       </c>
       <c r="J64" t="n">
         <v>7.75</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
       <c r="T64" t="n">
         <v>6</v>
       </c>
-      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
           <t>Creatinine (µmol/L) 0.03 ± 7.38 0.05 ± 7.02 -0.01 ± 7.75 0.983</t>
@@ -3696,35 +2954,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.38</v>
       </c>
       <c r="J65" t="n">
         <v>9.08</v>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
       <c r="T65" t="n">
         <v>6</v>
       </c>
-      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
           <t>e-GFR (ml/min/1.73m2) 0.38 ± 9.08 5.03 ± 22.52 0.50 ± 10.44 0.390</t>
@@ -3742,35 +2985,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>5.03</v>
       </c>
       <c r="J66" t="n">
         <v>22.52</v>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
       <c r="T66" t="n">
         <v>6</v>
       </c>
-      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
           <t>e-GFR (ml/min/1.73m2) 0.38 ± 9.08 5.03 ± 22.52 0.50 ± 10.44 0.390</t>
@@ -3788,35 +3016,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
         <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>10.44</v>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
       <c r="T67" t="n">
         <v>6</v>
       </c>
-      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
           <t>e-GFR (ml/min/1.73m2) 0.38 ± 9.08 5.03 ± 22.52 0.50 ± 10.44 0.390</t>
@@ -3834,35 +3047,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>0.57</v>
       </c>
       <c r="J68" t="n">
         <v>1.34</v>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
       <c r="T68" t="n">
         <v>6</v>
       </c>
-      <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr">
         <is>
           <t>E (kPa) -0.57 ± 1.34 -0.12 ± 0.90 -0.88 ± 1.52 0.029</t>
@@ -3880,35 +3078,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
         <v>0.12</v>
       </c>
       <c r="J69" t="n">
         <v>0.9</v>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
       <c r="T69" t="n">
         <v>6</v>
       </c>
-      <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr">
         <is>
           <t>E (kPa) -0.57 ± 1.34 -0.12 ± 0.90 -0.88 ± 1.52 0.029</t>
@@ -3926,35 +3109,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>0.88</v>
       </c>
       <c r="J70" t="n">
         <v>1.52</v>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
       <c r="T70" t="n">
         <v>6</v>
       </c>
-      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
         <is>
           <t>E (kPa) -0.57 ± 1.34 -0.12 ± 0.90 -0.88 ± 1.52 0.029</t>
@@ -3972,35 +3140,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>21.29</v>
       </c>
       <c r="J71" t="n">
         <v>32.66</v>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
       <c r="T71" t="n">
         <v>6</v>
       </c>
-      <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
           <t>CAP (dB/m) -21.29 ± 32.66 -7.86 ± 36.82 -30.39 ± 26.42 0.013</t>
@@ -4018,35 +3171,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
         <v>7.86</v>
       </c>
       <c r="J72" t="n">
         <v>36.82</v>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
       <c r="T72" t="n">
         <v>6</v>
       </c>
-      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr">
         <is>
           <t>CAP (dB/m) -21.29 ± 32.66 -7.86 ± 36.82 -30.39 ± 26.42 0.013</t>
@@ -4064,35 +3202,20 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>30.39</v>
       </c>
       <c r="J73" t="n">
         <v>26.42</v>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
       <c r="T73" t="n">
         <v>6</v>
       </c>
-      <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
         <is>
           <t>CAP (dB/m) -21.29 ± 32.66 -7.86 ± 36.82 -30.39 ± 26.42 0.013</t>
@@ -4101,6 +3224,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4184,7 +3308,6 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>ages or other third party material in this  or other third party material in this</t>
@@ -4220,7 +3343,6 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>age 
@@ -4257,7 +3379,6 @@
       <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>age 2 of 10 2 of 10</t>
@@ -4293,7 +3414,6 @@
       <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>aged 18–65 years; male  18–65 years; male</t>
@@ -4329,7 +3449,6 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>age 3 of 10 3 of 10</t>
@@ -4365,7 +3484,6 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>age BMI of patients in the orlistat group was  BMI of patients in the orlistat group was</t>
@@ -4401,7 +3519,6 @@
       <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>age 4 of 10 4 of 10</t>
@@ -4437,7 +3554,6 @@
       <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>age duration of gout ranged  duration of gout ranged</t>
@@ -4473,7 +3589,6 @@
       <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>age frequency of gout  frequency of gout</t>
@@ -4509,7 +3624,6 @@
       <c r="F11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>age of patients with gout flares  of patients with gout flares</t>
@@ -4545,7 +3659,6 @@
       <c r="F12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>age of patients  of patients</t>
@@ -4581,7 +3694,6 @@
       <c r="F13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>age 5 of 10 5 of 10</t>
@@ -4617,7 +3729,6 @@
       <c r="F14" t="n">
         <v>5</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Age at entry study (years) 37.00 (30.00,41.00) 37.00 (33.00,41.0 at entry study (years) 37.00 (30.00,41.00) 37.00 (33.00,41.0</t>
@@ -4653,7 +3764,6 @@
       <c r="F15" t="n">
         <v>5</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>TC (mmol/L) 5.29 ± 0.92 5.17 ± 0.87 5.41 ± 0.97 0.289</t>
@@ -4689,7 +3799,6 @@
       <c r="F16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>TC (mmol/L) 5.29 ± 0.92 5.17 ± 0.87 5.41 ± 0.97 0.289</t>
@@ -4725,7 +3834,6 @@
       <c r="F17" t="n">
         <v>5</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>TC (mmol/L) 5.29 ± 0.92 5.17 ± 0.87 5.41 ± 0.97 0.289</t>
@@ -4761,7 +3869,6 @@
       <c r="F18" t="n">
         <v>5</v>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>HDL (mmol/L) 1.02 ± 0.15 0.99 ± 0.15 1.04 ± 0.16 0.137</t>
@@ -4797,7 +3904,6 @@
       <c r="F19" t="n">
         <v>5</v>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>HDL (mmol/L) 1.02 ± 0.15 0.99 ± 0.15 1.04 ± 0.16 0.137</t>
@@ -4833,7 +3939,6 @@
       <c r="F20" t="n">
         <v>5</v>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>HDL (mmol/L) 1.02 ± 0.15 0.99 ± 0.15 1.04 ± 0.16 0.137</t>
@@ -4869,7 +3974,6 @@
       <c r="F21" t="n">
         <v>5</v>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>LDL (mmol/L) 3.48 ± 0.73 3.34 ± 0.68 3.62 ± 0.77 0.106</t>
@@ -4905,7 +4009,6 @@
       <c r="F22" t="n">
         <v>5</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>LDL (mmol/L) 3.48 ± 0.73 3.34 ± 0.68 3.62 ± 0.77 0.106</t>
@@ -4941,7 +4044,6 @@
       <c r="F23" t="n">
         <v>5</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>LDL (mmol/L) 3.48 ± 0.73 3.34 ± 0.68 3.62 ± 0.77 0.106</t>
@@ -4977,7 +4079,6 @@
       <c r="F24" t="n">
         <v>5</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>TG (mmol/L) 2.49 ± 1.09 2.47 ± 0.94 2.52 ± 1.23 0.844</t>
@@ -5013,7 +4114,6 @@
       <c r="F25" t="n">
         <v>5</v>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>TG (mmol/L) 2.49 ± 1.09 2.47 ± 0.94 2.52 ± 1.23 0.844</t>
@@ -5049,7 +4149,6 @@
       <c r="F26" t="n">
         <v>5</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>TG (mmol/L) 2.49 ± 1.09 2.47 ± 0.94 2.52 ± 1.23 0.844</t>
@@ -5085,7 +4184,6 @@
       <c r="F27" t="n">
         <v>5</v>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) 5.09 ± 0.49 5.09 ± 0.49 5.09 ± 0.50 0.964</t>
@@ -5121,7 +4219,6 @@
       <c r="F28" t="n">
         <v>5</v>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) 5.09 ± 0.49 5.09 ± 0.49 5.09 ± 0.50 0.964</t>
@@ -5157,7 +4254,6 @@
       <c r="F29" t="n">
         <v>5</v>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) 5.09 ± 0.49 5.09 ± 0.49 5.09 ± 0.50 0.964</t>
@@ -5193,7 +4289,6 @@
       <c r="F30" t="n">
         <v>5</v>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>ALT (U/L) 55.11 ± 33.04 52.82 ± 35.89 57.33 ± 30.35 0.569</t>
@@ -5229,7 +4324,6 @@
       <c r="F31" t="n">
         <v>5</v>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>ALT (U/L) 55.11 ± 33.04 52.82 ± 35.89 57.33 ± 30.35 0.569</t>
@@ -5265,7 +4359,6 @@
       <c r="F32" t="n">
         <v>5</v>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>ALT (U/L) 55.11 ± 33.04 52.82 ± 35.89 57.33 ± 30.35 0.569</t>
@@ -5301,7 +4394,6 @@
       <c r="F33" t="n">
         <v>5</v>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Urea (mmol/L) 4.45 ± 1.08 4.36 ± 1.22 4.54 ± 0.93 0.492</t>
@@ -5337,7 +4429,6 @@
       <c r="F34" t="n">
         <v>5</v>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Urea (mmol/L) 4.45 ± 1.08 4.36 ± 1.22 4.54 ± 0.93 0.492</t>
@@ -5373,7 +4464,6 @@
       <c r="F35" t="n">
         <v>5</v>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Urea (mmol/L) 4.45 ± 1.08 4.36 ± 1.22 4.54 ± 0.93 0.492</t>
@@ -5409,7 +4499,6 @@
       <c r="F36" t="n">
         <v>5</v>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Uric acid (mg/dl) 9.52 ± 1.60 9.51 ± 1.51 9.53 ± 1.81 0.956</t>
@@ -5445,7 +4534,6 @@
       <c r="F37" t="n">
         <v>5</v>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Uric acid (mg/dl) 9.52 ± 1.60 9.51 ± 1.51 9.53 ± 1.81 0.956</t>
@@ -5481,7 +4569,6 @@
       <c r="F38" t="n">
         <v>5</v>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Uric acid (mg/dl) 9.52 ± 1.60 9.51 ± 1.51 9.53 ± 1.81 0.956</t>
@@ -5517,7 +4604,6 @@
       <c r="F39" t="n">
         <v>5</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Aggregates 3.67 ± 3.88 3.61 ± 3.90 3.73 ± 3.91 0.905</t>
@@ -5553,7 +4639,6 @@
       <c r="F40" t="n">
         <v>5</v>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Aggregates 3.67 ± 3.88 3.61 ± 3.90 3.73 ± 3.91 0.905</t>
@@ -5589,7 +4674,6 @@
       <c r="F41" t="n">
         <v>5</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Aggregates 3.67 ± 3.88 3.61 ± 3.90 3.73 ± 3.91 0.905</t>
@@ -5625,7 +4709,6 @@
       <c r="F42" t="n">
         <v>5</v>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Double contour sign 1.15 ± 2.67 1.10 ± 2.68 1.20 ± 2.71 0.945</t>
@@ -5661,7 +4744,6 @@
       <c r="F43" t="n">
         <v>5</v>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Double contour sign 1.15 ± 2.67 1.10 ± 2.68 1.20 ± 2.71 0.945</t>
@@ -5697,7 +4779,6 @@
       <c r="F44" t="n">
         <v>5</v>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Double contour sign 1.15 ± 2.67 1.10 ± 2.68 1.20 ± 2.71 0.945</t>
@@ -5733,7 +4814,6 @@
       <c r="F45" t="n">
         <v>5</v>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Tophus 1.15 ± 2.99 1.13 ± 3.00 1.17 ± 3.04 0.961</t>
@@ -5769,7 +4849,6 @@
       <c r="F46" t="n">
         <v>5</v>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Tophus 1.15 ± 2.99 1.13 ± 3.00 1.17 ± 3.04 0.961</t>
@@ -5805,7 +4884,6 @@
       <c r="F47" t="n">
         <v>5</v>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Tophus 1.15 ± 2.99 1.13 ± 3.00 1.17 ± 3.04 0.961</t>
@@ -5841,7 +4919,6 @@
       <c r="F48" t="n">
         <v>5</v>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>The highest uric acid before (µmol/L) 628.01 ± 93.97 630.03 ± 94.57 626.22 ± 94.74 0.869</t>
@@ -5877,7 +4954,6 @@
       <c r="F49" t="n">
         <v>5</v>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>The highest uric acid before (µmol/L) 628.01 ± 93.97 630.03 ± 94.57 626.22 ± 94.74 0.869</t>
@@ -5913,7 +4989,6 @@
       <c r="F50" t="n">
         <v>5</v>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>The highest uric acid before (µmol/L) 628.01 ± 93.97 630.03 ± 94.57 626.22 ± 94.74 0.869</t>
@@ -5949,7 +5024,6 @@
       <c r="F51" t="n">
         <v>6</v>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>age 6 of 10 6 of 10</t>
@@ -5985,7 +5059,6 @@
       <c r="F52" t="n">
         <v>6</v>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>age of 2.85  kg of  of 2.85  kg of</t>
@@ -6021,7 +5094,6 @@
       <c r="F53" t="n">
         <v>6</v>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>ages of weight loss [ 21, 23].  of weight loss [ 21, 23].</t>
@@ -6057,7 +5129,6 @@
       <c r="F54" t="n">
         <v>6</v>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Weight (kg) -1.92 ± 2.59 -0.76 ± 2.37 -2.85 ± 2.37 0.001</t>
@@ -6093,7 +5164,6 @@
       <c r="F55" t="n">
         <v>6</v>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Weight (kg) -1.92 ± 2.59 -0.76 ± 2.37 -2.85 ± 2.37 0.001</t>
@@ -6129,7 +5199,6 @@
       <c r="F56" t="n">
         <v>6</v>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Weight (kg) -1.92 ± 2.59 -0.76 ± 2.37 -2.85 ± 2.37 0.001</t>
@@ -6165,7 +5234,6 @@
       <c r="F57" t="n">
         <v>6</v>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>BMI (kg/m2) -0.63 ± 0.83 -0.25 ± 0.75 -0.95 ± 0.77 0.001</t>
@@ -6201,7 +5269,6 @@
       <c r="F58" t="n">
         <v>6</v>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>BMI (kg/m2) -0.63 ± 0.83 -0.25 ± 0.75 -0.95 ± 0.77 0.001</t>
@@ -6237,7 +5304,6 @@
       <c r="F59" t="n">
         <v>6</v>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>BMI (kg/m2) -0.63 ± 0.83 -0.25 ± 0.75 -0.95 ± 0.77 0.001</t>
@@ -6273,7 +5339,6 @@
       <c r="F60" t="n">
         <v>6</v>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>WC (cm) -1.98 ± 2.67 -0.75 ± 2.60 -2.97 ± 2.32 0.001</t>
@@ -6309,7 +5374,6 @@
       <c r="F61" t="n">
         <v>6</v>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>WC (cm) -1.98 ± 2.67 -0.75 ± 2.60 -2.97 ± 2.32 0.001</t>
@@ -6345,7 +5409,6 @@
       <c r="F62" t="n">
         <v>6</v>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>WC (cm) -1.98 ± 2.67 -0.75 ± 2.60 -2.97 ± 2.32 0.001</t>
@@ -6381,7 +5444,6 @@
       <c r="F63" t="n">
         <v>6</v>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Body fat (kg) -1.39 ± 2.11 -0.19 ± 1.69 -2.30 ± 1.95 &lt;0.001</t>
@@ -6417,7 +5479,6 @@
       <c r="F64" t="n">
         <v>6</v>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Body fat (kg) -1.39 ± 2.11 -0.19 ± 1.69 -2.30 ± 1.95 &lt;0.001</t>
@@ -6453,7 +5514,6 @@
       <c r="F65" t="n">
         <v>6</v>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Body fat (kg) -1.39 ± 2.11 -0.19 ± 1.69 -2.30 ± 1.95 &lt;0.001</t>
@@ -6489,7 +5549,6 @@
       <c r="F66" t="n">
         <v>6</v>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Body muscle (kg) -0.42 ± 0.89 -0.09 ± 0.87 -0.67 ± 0.83 0.021</t>
@@ -6525,7 +5584,6 @@
       <c r="F67" t="n">
         <v>6</v>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Body muscle (kg) -0.42 ± 0.89 -0.09 ± 0.87 -0.67 ± 0.83 0.021</t>
@@ -6561,7 +5619,6 @@
       <c r="F68" t="n">
         <v>6</v>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Body muscle (kg) -0.42 ± 0.89 -0.09 ± 0.87 -0.67 ± 0.83 0.021</t>
@@ -6597,7 +5654,6 @@
       <c r="F69" t="n">
         <v>6</v>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) -0.06 ± 0.50 -0.03 ± 0.48 -0.07 ± 0.53 0.776</t>
@@ -6633,7 +5689,6 @@
       <c r="F70" t="n">
         <v>6</v>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) -0.06 ± 0.50 -0.03 ± 0.48 -0.07 ± 0.53 0.776</t>
@@ -6669,7 +5724,6 @@
       <c r="F71" t="n">
         <v>6</v>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Glucose (mmol/L) -0.06 ± 0.50 -0.03 ± 0.48 -0.07 ± 0.53 0.776</t>
@@ -6705,7 +5759,6 @@
       <c r="F72" t="n">
         <v>6</v>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>HDL (mmol/L) -0.05 ± 0.13 0.01 ± 0.13 -0.09 ± 0.10 0.002</t>
@@ -6741,7 +5794,6 @@
       <c r="F73" t="n">
         <v>6</v>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>HDL (mmol/L) -0.05 ± 0.13 0.01 ± 0.13 -0.09 ± 0.10 0.002</t>
@@ -6777,7 +5829,6 @@
       <c r="F74" t="n">
         <v>6</v>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>HDL (mmol/L) -0.05 ± 0.13 0.01 ± 0.13 -0.09 ± 0.10 0.002</t>
@@ -6813,7 +5864,6 @@
       <c r="F75" t="n">
         <v>6</v>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>TC (mmol/L) -0.39 ± 0.75 -0.10 ± 0.64 -0.61 ± 0.76 0.012</t>
@@ -6849,7 +5899,6 @@
       <c r="F76" t="n">
         <v>6</v>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>TC (mmol/L) -0.39 ± 0.75 -0.10 ± 0.64 -0.61 ± 0.76 0.012</t>
@@ -6885,7 +5934,6 @@
       <c r="F77" t="n">
         <v>6</v>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>TC (mmol/L) -0.39 ± 0.75 -0.10 ± 0.64 -0.61 ± 0.76 0.012</t>
@@ -6921,7 +5969,6 @@
       <c r="F78" t="n">
         <v>6</v>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Creatinine (µmol/L) 0.03 ± 7.38 0.05 ± 7.02 -0.01 ± 7.75 0.983</t>
@@ -6957,7 +6004,6 @@
       <c r="F79" t="n">
         <v>6</v>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Creatinine (µmol/L) 0.03 ± 7.38 0.05 ± 7.02 -0.01 ± 7.75 0.983</t>
@@ -6993,7 +6039,6 @@
       <c r="F80" t="n">
         <v>6</v>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Creatinine (µmol/L) 0.03 ± 7.38 0.05 ± 7.02 -0.01 ± 7.75 0.983</t>
@@ -7029,7 +6074,6 @@
       <c r="F81" t="n">
         <v>6</v>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>e-GFR (ml/min/1.73m2) 0.38 ± 9.08 5.03 ± 22.52 0.50 ± 10.44 0.390</t>
@@ -7065,7 +6109,6 @@
       <c r="F82" t="n">
         <v>6</v>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>e-GFR (ml/min/1.73m2) 0.38 ± 9.08 5.03 ± 22.52 0.50 ± 10.44 0.390</t>
@@ -7101,7 +6144,6 @@
       <c r="F83" t="n">
         <v>6</v>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>e-GFR (ml/min/1.73m2) 0.38 ± 9.08 5.03 ± 22.52 0.50 ± 10.44 0.390</t>
@@ -7137,7 +6179,6 @@
       <c r="F84" t="n">
         <v>6</v>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>E (kPa) -0.57 ± 1.34 -0.12 ± 0.90 -0.88 ± 1.52 0.029</t>
@@ -7173,7 +6214,6 @@
       <c r="F85" t="n">
         <v>6</v>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>E (kPa) -0.57 ± 1.34 -0.12 ± 0.90 -0.88 ± 1.52 0.029</t>
@@ -7209,7 +6249,6 @@
       <c r="F86" t="n">
         <v>6</v>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>E (kPa) -0.57 ± 1.34 -0.12 ± 0.90 -0.88 ± 1.52 0.029</t>
@@ -7245,7 +6284,6 @@
       <c r="F87" t="n">
         <v>6</v>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>CAP (dB/m) -21.29 ± 32.66 -7.86 ± 36.82 -30.39 ± 26.42 0.013</t>
@@ -7281,7 +6319,6 @@
       <c r="F88" t="n">
         <v>6</v>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>CAP (dB/m) -21.29 ± 32.66 -7.86 ± 36.82 -30.39 ± 26.42 0.013</t>
@@ -7317,7 +6354,6 @@
       <c r="F89" t="n">
         <v>6</v>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>CAP (dB/m) -21.29 ± 32.66 -7.86 ± 36.82 -30.39 ± 26.42 0.013</t>
@@ -7353,7 +6389,6 @@
       <c r="F90" t="n">
         <v>7</v>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>age 7 of 10 7 of 10</t>
@@ -7389,7 +6424,6 @@
       <c r="F91" t="n">
         <v>7</v>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>age in obese  in obese</t>
@@ -7425,7 +6459,6 @@
       <c r="F92" t="n">
         <v>7</v>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>ages [ 27]. Activation of  [ 27]. Activation of</t>
@@ -7461,7 +6494,6 @@
       <c r="F93" t="n">
         <v>7</v>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>ages of weight loss. of weight loss.</t>
@@ -7497,7 +6529,6 @@
       <c r="F94" t="n">
         <v>7</v>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>age reduction in SUA lev - reduction in SUA lev -</t>
@@ -7533,7 +6564,6 @@
       <c r="F95" t="n">
         <v>7</v>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>age of patients who experienced gout flares in both groups. (A)  of patients who experienced gout flares in both groups. (A)</t>
@@ -7569,7 +6599,6 @@
       <c r="F96" t="n">
         <v>8</v>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>age 8 of 10 8 of 10</t>
@@ -7605,7 +6634,6 @@
       <c r="F97" t="n">
         <v>9</v>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>age 9 of 10 9 of 10</t>
@@ -7641,7 +6669,6 @@
       <c r="F98" t="n">
         <v>9</v>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>ages of  of</t>
@@ -7677,7 +6704,6 @@
       <c r="F99" t="n">
         <v>9</v>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>age of weight loss. Further studies are needed to  of weight loss. Further studies are needed to</t>
@@ -7713,7 +6739,6 @@
       <c r="F100" t="n">
         <v>10</v>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>age 10 of 10 10 of 10</t>
@@ -7749,7 +6774,6 @@
       <c r="F101" t="n">
         <v>10</v>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>age via NF-κβ-  via NF-κβ-</t>
@@ -7785,7 +6809,6 @@
       <c r="F102" t="n">
         <v>10</v>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>ages in obese severe Acute  in obese severe Acute</t>
@@ -7821,7 +6844,6 @@
       <c r="F103" t="n">
         <v>10</v>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>age asymptomatic hyperuricemia? Joint Bone  asymptomatic hyperuricemia? Joint Bone</t>
@@ -7830,6 +6852,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7890,7 +6913,6 @@
           <t>ISS_0001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Studies</t>
@@ -7928,7 +6950,6 @@
           <t>ISS_0002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Eligibility</t>
@@ -7966,7 +6987,6 @@
           <t>ISS_0003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Outcomes</t>
@@ -8004,7 +7024,6 @@
           <t>ISS_0004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Provenance</t>
@@ -8038,6 +7057,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8128,25 +7148,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>5.29</v>
       </c>
       <c r="J2" t="n">
         <v>0.92</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8154,25 +7164,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>5.17</v>
       </c>
       <c r="J3" t="n">
         <v>0.87</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8180,25 +7180,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>5.41</v>
       </c>
       <c r="J4" t="n">
         <v>0.97</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8206,25 +7196,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>1.02</v>
       </c>
       <c r="J5" t="n">
         <v>0.15</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8232,25 +7212,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>0.99</v>
       </c>
       <c r="J6" t="n">
         <v>0.15</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8258,25 +7228,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>1.04</v>
       </c>
       <c r="J7" t="n">
         <v>0.16</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8284,25 +7244,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>3.48</v>
       </c>
       <c r="J8" t="n">
         <v>0.73</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8310,25 +7260,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>3.34</v>
       </c>
       <c r="J9" t="n">
         <v>0.68</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5</v>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8336,25 +7276,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>3.62</v>
       </c>
       <c r="J10" t="n">
         <v>0.77</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8362,25 +7292,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>2.49</v>
       </c>
       <c r="J11" t="n">
         <v>1.09</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8388,25 +7308,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>2.47</v>
       </c>
       <c r="J12" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>5</v>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8414,25 +7324,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>2.52</v>
       </c>
       <c r="J13" t="n">
         <v>1.23</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8440,25 +7340,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>5.09</v>
       </c>
       <c r="J14" t="n">
         <v>0.49</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>5</v>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8466,25 +7356,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>5.09</v>
       </c>
       <c r="J15" t="n">
         <v>0.49</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>5</v>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8492,25 +7372,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>5.09</v>
       </c>
       <c r="J16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>5</v>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8518,25 +7388,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>55.11</v>
       </c>
       <c r="J17" t="n">
         <v>33.04</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>5</v>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8544,25 +7404,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>52.82</v>
       </c>
       <c r="J18" t="n">
         <v>35.89</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>5</v>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8570,25 +7420,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>57.33</v>
       </c>
       <c r="J19" t="n">
         <v>30.35</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>5</v>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8596,25 +7436,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>4.45</v>
       </c>
       <c r="J20" t="n">
         <v>1.08</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8622,25 +7452,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>4.36</v>
       </c>
       <c r="J21" t="n">
         <v>1.22</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>5</v>
       </c>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8648,25 +7468,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>4.54</v>
       </c>
       <c r="J22" t="n">
         <v>0.93</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>5</v>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8674,25 +7484,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>9.52</v>
       </c>
       <c r="J23" t="n">
         <v>1.6</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>5</v>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8700,25 +7500,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>9.51</v>
       </c>
       <c r="J24" t="n">
         <v>1.51</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>5</v>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8726,25 +7516,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>9.529999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>1.81</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>5</v>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8752,25 +7532,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>3.67</v>
       </c>
       <c r="J26" t="n">
         <v>3.88</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>5</v>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8778,25 +7548,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>3.61</v>
       </c>
       <c r="J27" t="n">
         <v>3.9</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>5</v>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8804,25 +7564,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>3.73</v>
       </c>
       <c r="J28" t="n">
         <v>3.91</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>5</v>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8830,25 +7580,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>1.15</v>
       </c>
       <c r="J29" t="n">
         <v>2.67</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>5</v>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8856,25 +7596,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>2.68</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>5</v>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8882,25 +7612,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>2.71</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
         <v>5</v>
       </c>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8908,25 +7628,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
         <v>1.15</v>
       </c>
       <c r="J32" t="n">
         <v>2.99</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>5</v>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8934,25 +7644,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
         <v>1.13</v>
       </c>
       <c r="J33" t="n">
         <v>3</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>5</v>
       </c>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8960,25 +7660,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>1.17</v>
       </c>
       <c r="J34" t="n">
         <v>3.04</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8986,25 +7676,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
         <v>628.01</v>
       </c>
       <c r="J35" t="n">
         <v>93.97</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>5</v>
       </c>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9012,25 +7692,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
         <v>630.03</v>
       </c>
       <c r="J36" t="n">
         <v>94.56999999999999</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>5</v>
       </c>
-      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9038,25 +7708,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
         <v>626.22</v>
       </c>
       <c r="J37" t="n">
         <v>94.73999999999999</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
         <v>5</v>
       </c>
-      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9064,25 +7724,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>1.92</v>
       </c>
       <c r="J38" t="n">
         <v>2.59</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>6</v>
       </c>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9090,25 +7740,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>0.76</v>
       </c>
       <c r="J39" t="n">
         <v>2.37</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>6</v>
       </c>
-      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9116,25 +7756,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>2.85</v>
       </c>
       <c r="J40" t="n">
         <v>2.37</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>6</v>
       </c>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9142,25 +7772,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>0.63</v>
       </c>
       <c r="J41" t="n">
         <v>0.83</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>6</v>
       </c>
-      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9168,25 +7788,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>0.25</v>
       </c>
       <c r="J42" t="n">
         <v>0.75</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>6</v>
       </c>
-      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9194,25 +7804,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>0.95</v>
       </c>
       <c r="J43" t="n">
         <v>0.77</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>6</v>
       </c>
-      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9220,25 +7820,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>1.98</v>
       </c>
       <c r="J44" t="n">
         <v>2.67</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>6</v>
       </c>
-      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9246,25 +7836,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>0.75</v>
       </c>
       <c r="J45" t="n">
         <v>2.6</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>6</v>
       </c>
-      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9272,25 +7852,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>2.97</v>
       </c>
       <c r="J46" t="n">
         <v>2.32</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>6</v>
       </c>
-      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9298,25 +7868,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>1.39</v>
       </c>
       <c r="J47" t="n">
         <v>2.11</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>6</v>
       </c>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9324,25 +7884,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>0.19</v>
       </c>
       <c r="J48" t="n">
         <v>1.69</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>6</v>
       </c>
-      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9350,25 +7900,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>1.95</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
         <v>6</v>
       </c>
-      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9376,25 +7916,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>0.42</v>
       </c>
       <c r="J50" t="n">
         <v>0.89</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>6</v>
       </c>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9402,25 +7932,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>0.09</v>
       </c>
       <c r="J51" t="n">
         <v>0.87</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>6</v>
       </c>
-      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9428,25 +7948,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>0.67</v>
       </c>
       <c r="J52" t="n">
         <v>0.83</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
         <v>6</v>
       </c>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9454,25 +7964,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>0.06</v>
       </c>
       <c r="J53" t="n">
         <v>0.5</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
         <v>6</v>
       </c>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9480,25 +7980,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>0.03</v>
       </c>
       <c r="J54" t="n">
         <v>0.48</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
         <v>6</v>
       </c>
-      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9506,25 +7996,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0.53</v>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
         <v>6</v>
       </c>
-      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9532,25 +8012,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>0.05</v>
       </c>
       <c r="J56" t="n">
         <v>0.13</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>6</v>
       </c>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9558,25 +8028,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>0.01</v>
       </c>
       <c r="J57" t="n">
         <v>0.13</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
         <v>6</v>
       </c>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9584,25 +8044,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>0.09</v>
       </c>
       <c r="J58" t="n">
         <v>0.1</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
         <v>6</v>
       </c>
-      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9610,25 +8060,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>0.39</v>
       </c>
       <c r="J59" t="n">
         <v>0.75</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>6</v>
       </c>
-      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9636,25 +8076,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0.1</v>
       </c>
       <c r="J60" t="n">
         <v>0.64</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
         <v>6</v>
       </c>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9662,25 +8092,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.61</v>
       </c>
       <c r="J61" t="n">
         <v>0.76</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>6</v>
       </c>
-      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9688,25 +8108,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0.03</v>
       </c>
       <c r="J62" t="n">
         <v>7.38</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
         <v>6</v>
       </c>
-      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9714,25 +8124,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0.05</v>
       </c>
       <c r="J63" t="n">
         <v>7.02</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
         <v>6</v>
       </c>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9740,25 +8140,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0.01</v>
       </c>
       <c r="J64" t="n">
         <v>7.75</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>6</v>
       </c>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9766,25 +8156,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.38</v>
       </c>
       <c r="J65" t="n">
         <v>9.08</v>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
         <v>6</v>
       </c>
-      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9792,25 +8172,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>5.03</v>
       </c>
       <c r="J66" t="n">
         <v>22.52</v>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
         <v>6</v>
       </c>
-      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9818,25 +8188,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
         <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>10.44</v>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
         <v>6</v>
       </c>
-      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9844,25 +8204,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>0.57</v>
       </c>
       <c r="J68" t="n">
         <v>1.34</v>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
         <v>6</v>
       </c>
-      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9870,25 +8220,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
         <v>0.12</v>
       </c>
       <c r="J69" t="n">
         <v>0.9</v>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
         <v>6</v>
       </c>
-      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9896,25 +8236,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>0.88</v>
       </c>
       <c r="J70" t="n">
         <v>1.52</v>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>6</v>
       </c>
-      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9922,25 +8252,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>21.29</v>
       </c>
       <c r="J71" t="n">
         <v>32.66</v>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>6</v>
       </c>
-      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9948,25 +8268,15 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
         <v>7.86</v>
       </c>
       <c r="J72" t="n">
         <v>36.82</v>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
         <v>6</v>
       </c>
-      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9974,27 +8284,18 @@
           <t>RCT_ORLISTAT</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>30.39</v>
       </c>
       <c r="J73" t="n">
         <v>26.42</v>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>6</v>
       </c>
-      <c r="N73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>